--- a/DOSSIES_MULTIFORMATO/SUL_AMERICA/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SUL_AMERICA/dossie.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
     </row>
